--- a/docs/export-templates/AI问书_全域机构账户数据导出.xlsx
+++ b/docs/export-templates/AI问书_全域机构账户数据导出.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="91">
   <si>
     <t>平台机构账户</t>
   </si>
@@ -28,6 +28,9 @@
     <t>账户名</t>
   </si>
   <si>
+    <t>密码</t>
+  </si>
+  <si>
     <t>姓名</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>admin01</t>
   </si>
   <si>
+    <t>Xk7mPq2a</t>
+  </si>
+  <si>
     <t>张三</t>
   </si>
   <si>
@@ -76,6 +82,9 @@
     <t>view01</t>
   </si>
   <si>
+    <t>Vw3nRt8b</t>
+  </si>
+  <si>
     <t>李四</t>
   </si>
   <si>
@@ -97,6 +106,9 @@
     <t>ops01</t>
   </si>
   <si>
+    <t>Hy6sLd4c</t>
+  </si>
+  <si>
     <t>王五</t>
   </si>
   <si>
@@ -115,6 +127,9 @@
     <t>admin02</t>
   </si>
   <si>
+    <t>Qe9jBn5d</t>
+  </si>
+  <si>
     <t>赵敏</t>
   </si>
   <si>
@@ -127,6 +142,9 @@
     <t>ops02</t>
   </si>
   <si>
+    <t>Mz2kTw7e</t>
+  </si>
+  <si>
     <t>钱进</t>
   </si>
   <si>
@@ -139,6 +157,9 @@
     <t>view02</t>
   </si>
   <si>
+    <t>Fp8rGh3f</t>
+  </si>
+  <si>
     <t>孙莉</t>
   </si>
   <si>
@@ -151,6 +172,9 @@
     <t>ops03</t>
   </si>
   <si>
+    <t>Ld5vNc9g</t>
+  </si>
+  <si>
     <t>周涛</t>
   </si>
   <si>
@@ -163,6 +187,9 @@
     <t>admin03</t>
   </si>
   <si>
+    <t>Rb4xJm6h</t>
+  </si>
+  <si>
     <t>吴芳</t>
   </si>
   <si>
@@ -175,6 +202,9 @@
     <t>view03</t>
   </si>
   <si>
+    <t>Tn7qWs2j</t>
+  </si>
+  <si>
     <t>郑昊</t>
   </si>
   <si>
@@ -187,6 +217,9 @@
     <t>ops04</t>
   </si>
   <si>
+    <t>Gc3yKp8k</t>
+  </si>
+  <si>
     <t>冯雪</t>
   </si>
   <si>
@@ -199,6 +232,9 @@
     <t>admin04</t>
   </si>
   <si>
+    <t>Wj6hZr4m</t>
+  </si>
+  <si>
     <t>陈晨</t>
   </si>
   <si>
@@ -211,6 +247,9 @@
     <t>view04</t>
   </si>
   <si>
+    <t>Nd9fXb5n</t>
+  </si>
+  <si>
     <t>褚岩</t>
   </si>
   <si>
@@ -223,6 +262,9 @@
     <t>ops05</t>
   </si>
   <si>
+    <t>Ks2tCv7p</t>
+  </si>
+  <si>
     <t>卫东</t>
   </si>
   <si>
@@ -233,6 +275,9 @@
   </si>
   <si>
     <t>admin05</t>
+  </si>
+  <si>
+    <t>Yh8gMd3q</t>
   </si>
   <si>
     <t>蒋琳</t>
@@ -705,19 +750,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -728,8 +773,9 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" ht="25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -740,8 +786,9 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -752,8 +799,9 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -778,377 +826,422 @@
       <c r="H4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="G9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="H12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="7" t="s">
+      <c r="I12" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="F14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="H16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="G17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="F18" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>75</v>
+        <v>19</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H4"/>
+  <autoFilter ref="A4:I4"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
